--- a/public/발주_기본품목_템플릿.xlsx
+++ b/public/발주_기본품목_템플릿.xlsx
@@ -11,9 +11,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="18">
   <si>
-    <t>발주 유형</t>
+    <t>목재발주</t>
   </si>
   <si>
     <t>품목</t>
@@ -32,9 +32,6 @@
   </si>
   <si>
     <t>비고</t>
-  </si>
-  <si>
-    <t>목재발주</t>
   </si>
   <si>
     <t/>
@@ -444,283 +441,1382 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:F77"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="C2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="D2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="E2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="F2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>9</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" t="s">
+        <v>4</v>
+      </c>
+      <c r="E16" t="s">
+        <v>5</v>
+      </c>
+      <c r="F16" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" t="s">
+        <v>7</v>
+      </c>
+      <c r="F19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>10</v>
       </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>1</v>
+      </c>
+      <c r="B23" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" t="s">
+        <v>4</v>
+      </c>
+      <c r="E23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" t="s">
+        <v>7</v>
+      </c>
+      <c r="F24" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" t="s">
+        <v>7</v>
+      </c>
+      <c r="F25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" t="s">
+        <v>7</v>
+      </c>
+      <c r="F27" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" t="s">
+        <v>7</v>
+      </c>
+      <c r="E28" t="s">
+        <v>7</v>
+      </c>
+      <c r="F28" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>11</v>
       </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>1</v>
+      </c>
+      <c r="B30" t="s">
+        <v>2</v>
+      </c>
+      <c r="C30" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" t="s">
+        <v>4</v>
+      </c>
+      <c r="E30" t="s">
+        <v>5</v>
+      </c>
+      <c r="F30" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" t="s">
+        <v>7</v>
+      </c>
+      <c r="E31" t="s">
+        <v>7</v>
+      </c>
+      <c r="F31" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" t="s">
+        <v>7</v>
+      </c>
+      <c r="E32" t="s">
+        <v>7</v>
+      </c>
+      <c r="F32" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" t="s">
+        <v>7</v>
+      </c>
+      <c r="D33" t="s">
+        <v>7</v>
+      </c>
+      <c r="E33" t="s">
+        <v>7</v>
+      </c>
+      <c r="F33" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" t="s">
+        <v>7</v>
+      </c>
+      <c r="E34" t="s">
+        <v>7</v>
+      </c>
+      <c r="F34" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" t="s">
+        <v>7</v>
+      </c>
+      <c r="E35" t="s">
+        <v>7</v>
+      </c>
+      <c r="F35" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>12</v>
       </c>
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>8</v>
-      </c>
-      <c r="G6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B37" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" t="s">
+        <v>3</v>
+      </c>
+      <c r="D37" t="s">
+        <v>4</v>
+      </c>
+      <c r="E37" t="s">
+        <v>5</v>
+      </c>
+      <c r="F37" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" t="s">
+        <v>7</v>
+      </c>
+      <c r="E38" t="s">
+        <v>7</v>
+      </c>
+      <c r="F38" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>7</v>
+      </c>
+      <c r="B39" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39" t="s">
+        <v>7</v>
+      </c>
+      <c r="E39" t="s">
+        <v>7</v>
+      </c>
+      <c r="F39" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>7</v>
+      </c>
+      <c r="B40" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" t="s">
+        <v>7</v>
+      </c>
+      <c r="E40" t="s">
+        <v>7</v>
+      </c>
+      <c r="F40" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>7</v>
+      </c>
+      <c r="B41" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" t="s">
+        <v>7</v>
+      </c>
+      <c r="E41" t="s">
+        <v>7</v>
+      </c>
+      <c r="F41" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>7</v>
+      </c>
+      <c r="B42" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" t="s">
+        <v>7</v>
+      </c>
+      <c r="E42" t="s">
+        <v>7</v>
+      </c>
+      <c r="F42" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>13</v>
       </c>
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>1</v>
+      </c>
+      <c r="B44" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" t="s">
+        <v>3</v>
+      </c>
+      <c r="D44" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>7</v>
+      </c>
+      <c r="B45" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" t="s">
+        <v>7</v>
+      </c>
+      <c r="D45" t="s">
+        <v>7</v>
+      </c>
+      <c r="E45" t="s">
+        <v>7</v>
+      </c>
+      <c r="F45" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>7</v>
+      </c>
+      <c r="B46" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" t="s">
+        <v>7</v>
+      </c>
+      <c r="D46" t="s">
+        <v>7</v>
+      </c>
+      <c r="E46" t="s">
+        <v>7</v>
+      </c>
+      <c r="F46" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>7</v>
+      </c>
+      <c r="B47" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" t="s">
+        <v>7</v>
+      </c>
+      <c r="D47" t="s">
+        <v>7</v>
+      </c>
+      <c r="E47" t="s">
+        <v>7</v>
+      </c>
+      <c r="F47" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>7</v>
+      </c>
+      <c r="B48" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" t="s">
+        <v>7</v>
+      </c>
+      <c r="D48" t="s">
+        <v>7</v>
+      </c>
+      <c r="E48" t="s">
+        <v>7</v>
+      </c>
+      <c r="F48" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>7</v>
+      </c>
+      <c r="B49" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" t="s">
+        <v>7</v>
+      </c>
+      <c r="D49" t="s">
+        <v>7</v>
+      </c>
+      <c r="E49" t="s">
+        <v>7</v>
+      </c>
+      <c r="F49" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>14</v>
       </c>
-      <c r="B8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>1</v>
+      </c>
+      <c r="B51" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" t="s">
+        <v>3</v>
+      </c>
+      <c r="D51" t="s">
+        <v>4</v>
+      </c>
+      <c r="E51" t="s">
+        <v>5</v>
+      </c>
+      <c r="F51" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>7</v>
+      </c>
+      <c r="B52" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" t="s">
+        <v>7</v>
+      </c>
+      <c r="D52" t="s">
+        <v>7</v>
+      </c>
+      <c r="E52" t="s">
+        <v>7</v>
+      </c>
+      <c r="F52" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>7</v>
+      </c>
+      <c r="B53" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" t="s">
+        <v>7</v>
+      </c>
+      <c r="D53" t="s">
+        <v>7</v>
+      </c>
+      <c r="E53" t="s">
+        <v>7</v>
+      </c>
+      <c r="F53" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>7</v>
+      </c>
+      <c r="B54" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" t="s">
+        <v>7</v>
+      </c>
+      <c r="D54" t="s">
+        <v>7</v>
+      </c>
+      <c r="E54" t="s">
+        <v>7</v>
+      </c>
+      <c r="F54" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>7</v>
+      </c>
+      <c r="B55" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" t="s">
+        <v>7</v>
+      </c>
+      <c r="D55" t="s">
+        <v>7</v>
+      </c>
+      <c r="E55" t="s">
+        <v>7</v>
+      </c>
+      <c r="F55" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>7</v>
+      </c>
+      <c r="B56" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" t="s">
+        <v>7</v>
+      </c>
+      <c r="D56" t="s">
+        <v>7</v>
+      </c>
+      <c r="E56" t="s">
+        <v>7</v>
+      </c>
+      <c r="F56" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
         <v>15</v>
       </c>
-      <c r="B9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>8</v>
-      </c>
-      <c r="G9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>1</v>
+      </c>
+      <c r="B58" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" t="s">
+        <v>3</v>
+      </c>
+      <c r="D58" t="s">
+        <v>4</v>
+      </c>
+      <c r="E58" t="s">
+        <v>5</v>
+      </c>
+      <c r="F58" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>7</v>
+      </c>
+      <c r="B59" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" t="s">
+        <v>7</v>
+      </c>
+      <c r="D59" t="s">
+        <v>7</v>
+      </c>
+      <c r="E59" t="s">
+        <v>7</v>
+      </c>
+      <c r="F59" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>7</v>
+      </c>
+      <c r="B60" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" t="s">
+        <v>7</v>
+      </c>
+      <c r="D60" t="s">
+        <v>7</v>
+      </c>
+      <c r="E60" t="s">
+        <v>7</v>
+      </c>
+      <c r="F60" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>7</v>
+      </c>
+      <c r="B61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" t="s">
+        <v>7</v>
+      </c>
+      <c r="D61" t="s">
+        <v>7</v>
+      </c>
+      <c r="E61" t="s">
+        <v>7</v>
+      </c>
+      <c r="F61" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>7</v>
+      </c>
+      <c r="B62" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" t="s">
+        <v>7</v>
+      </c>
+      <c r="D62" t="s">
+        <v>7</v>
+      </c>
+      <c r="E62" t="s">
+        <v>7</v>
+      </c>
+      <c r="F62" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>7</v>
+      </c>
+      <c r="B63" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" t="s">
+        <v>7</v>
+      </c>
+      <c r="D63" t="s">
+        <v>7</v>
+      </c>
+      <c r="E63" t="s">
+        <v>7</v>
+      </c>
+      <c r="F63" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
         <v>16</v>
       </c>
-      <c r="B10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>8</v>
-      </c>
-      <c r="G10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>1</v>
+      </c>
+      <c r="B65" t="s">
+        <v>2</v>
+      </c>
+      <c r="C65" t="s">
+        <v>3</v>
+      </c>
+      <c r="D65" t="s">
+        <v>4</v>
+      </c>
+      <c r="E65" t="s">
+        <v>5</v>
+      </c>
+      <c r="F65" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>7</v>
+      </c>
+      <c r="B66" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" t="s">
+        <v>7</v>
+      </c>
+      <c r="D66" t="s">
+        <v>7</v>
+      </c>
+      <c r="E66" t="s">
+        <v>7</v>
+      </c>
+      <c r="F66" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>7</v>
+      </c>
+      <c r="B67" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" t="s">
+        <v>7</v>
+      </c>
+      <c r="D67" t="s">
+        <v>7</v>
+      </c>
+      <c r="E67" t="s">
+        <v>7</v>
+      </c>
+      <c r="F67" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>7</v>
+      </c>
+      <c r="B68" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" t="s">
+        <v>7</v>
+      </c>
+      <c r="D68" t="s">
+        <v>7</v>
+      </c>
+      <c r="E68" t="s">
+        <v>7</v>
+      </c>
+      <c r="F68" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>7</v>
+      </c>
+      <c r="B69" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" t="s">
+        <v>7</v>
+      </c>
+      <c r="D69" t="s">
+        <v>7</v>
+      </c>
+      <c r="E69" t="s">
+        <v>7</v>
+      </c>
+      <c r="F69" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>7</v>
+      </c>
+      <c r="B70" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" t="s">
+        <v>7</v>
+      </c>
+      <c r="D70" t="s">
+        <v>7</v>
+      </c>
+      <c r="E70" t="s">
+        <v>7</v>
+      </c>
+      <c r="F70" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
         <v>17</v>
       </c>
-      <c r="B11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>8</v>
-      </c>
-      <c r="G11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>8</v>
-      </c>
-      <c r="G12" t="s">
-        <v>8</v>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>1</v>
+      </c>
+      <c r="B72" t="s">
+        <v>2</v>
+      </c>
+      <c r="C72" t="s">
+        <v>3</v>
+      </c>
+      <c r="D72" t="s">
+        <v>4</v>
+      </c>
+      <c r="E72" t="s">
+        <v>5</v>
+      </c>
+      <c r="F72" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>7</v>
+      </c>
+      <c r="B73" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73" t="s">
+        <v>7</v>
+      </c>
+      <c r="D73" t="s">
+        <v>7</v>
+      </c>
+      <c r="E73" t="s">
+        <v>7</v>
+      </c>
+      <c r="F73" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>7</v>
+      </c>
+      <c r="B74" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" t="s">
+        <v>7</v>
+      </c>
+      <c r="D74" t="s">
+        <v>7</v>
+      </c>
+      <c r="E74" t="s">
+        <v>7</v>
+      </c>
+      <c r="F74" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>7</v>
+      </c>
+      <c r="B75" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" t="s">
+        <v>7</v>
+      </c>
+      <c r="D75" t="s">
+        <v>7</v>
+      </c>
+      <c r="E75" t="s">
+        <v>7</v>
+      </c>
+      <c r="F75" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>7</v>
+      </c>
+      <c r="B76" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76" t="s">
+        <v>7</v>
+      </c>
+      <c r="D76" t="s">
+        <v>7</v>
+      </c>
+      <c r="E76" t="s">
+        <v>7</v>
+      </c>
+      <c r="F76" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>7</v>
+      </c>
+      <c r="B77" t="s">
+        <v>7</v>
+      </c>
+      <c r="C77" t="s">
+        <v>7</v>
+      </c>
+      <c r="D77" t="s">
+        <v>7</v>
+      </c>
+      <c r="E77" t="s">
+        <v>7</v>
+      </c>
+      <c r="F77" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
